--- a/docs/Checklist-CEDI-Madrid.xlsx
+++ b/docs/Checklist-CEDI-Madrid.xlsx
@@ -36,7 +36,7 @@
     <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Titles" vbProcedure="false">'6 Seguimiento pedidos'!$32:$32</definedName>
     <definedName function="false" hidden="false" localSheetId="8" name="_xlnm.Print_Titles" vbProcedure="false">'7 Prioridades'!$40:$40</definedName>
     <definedName function="false" hidden="false" localSheetId="9" name="_xlnm.Print_Titles" vbProcedure="false">'8 Muelle y cargue'!$32:$32</definedName>
-    <definedName function="false" hidden="false" localSheetId="10" name="_xlnm.Print_Titles" vbProcedure="false">'9 Preguntas'!$19:$19</definedName>
+    <definedName function="false" hidden="false" localSheetId="10" name="_xlnm.Print_Titles" vbProcedure="false">'9 Preguntas'!$24:$24</definedName>
     <definedName function="false" hidden="false" localSheetId="14" name="_xlnm.Print_Titles" vbProcedure="false">Glosario!$4:$4</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">Resumen!$4:$4</definedName>
   </definedNames>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="995">
   <si>
     <t xml:space="preserve">EVALUACIÓN OPERATIVA — CEDI MADRID</t>
   </si>
@@ -1600,7 +1600,7 @@
     <t xml:space="preserve">9 · PREGUNTAS PARA HACER EN PISO</t>
   </si>
   <si>
-    <t xml:space="preserve">Formuladas tal como se dicen. Cada una trae qué buscar en la respuesta y qué hacer si aparece la señal de alarma.</t>
+    <t xml:space="preserve">Lo respondido en el recorrido queda escrito. Lo que falta está marcado como Pendiente: filtra por esa columna y esa es tu agenda de la reunión.</t>
   </si>
   <si>
     <t xml:space="preserve">  REGLA GENERAL</t>
@@ -1615,7 +1615,10 @@
     <t xml:space="preserve">Nunca preguntes «¿quién se equivocó?». Cierra la información para el resto del día y para la próxima visita.</t>
   </si>
   <si>
-    <t xml:space="preserve">La operación trabaja con dos WMS, uno para el CD centralizado y otro para el descentralizado. Las preguntas marcadas «Dos WMS» tienen ese marco: pregúntalas siempre precisando de cuál de los dos estás hablando.</t>
+    <t xml:space="preserve">La operación trabaja con dos sistemas, EWM y WMS. Las preguntas marcadas «Dos WMS» tienen ese marco: pregúntalas siempre precisando de cuál de los dos estás hablando.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una respuesta de la jefatura no reemplaza la del operario. Las preguntas del grupo «Operario» siguen pendientes aunque el jefe ya haya opinado sobre lo mismo.</t>
   </si>
   <si>
     <t xml:space="preserve">  PREGUNTAS QUE NO FUNCIONAN Y CON QUÉ REEMPLAZARLAS</t>
@@ -1663,6 +1666,24 @@
     <t xml:space="preserve">«Muéstreme un pedido que se alistó temprano y salió tarde. ¿Qué pasó?»</t>
   </si>
   <si>
+    <t xml:space="preserve">  AVANCE DEL CUESTIONARIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total preguntas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respondidas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pendientes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% pendiente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filtra la columna Estado por «Pendiente» y esa es la agenda de la reunión. La columna Prioridad ordena por dónde empezar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  BANCO DE PREGUNTAS</t>
   </si>
   <si>
@@ -1675,6 +1696,9 @@
     <t xml:space="preserve">Por qué esta pregunta</t>
   </si>
   <si>
+    <t xml:space="preserve">Fuente</t>
+  </si>
+  <si>
     <t xml:space="preserve">Qué hacer si aparece la señal</t>
   </si>
   <si>
@@ -1687,6 +1711,9 @@
     <t xml:space="preserve">Define si va adelante o detrás del alistamiento.</t>
   </si>
   <si>
+    <t xml:space="preserve">Pendiente</t>
+  </si>
+  <si>
     <t xml:space="preserve">Responden «a demanda» o «cuando avisan».</t>
   </si>
   <si>
@@ -1711,6 +1738,9 @@
     <t xml:space="preserve">Revela si hay regla o improvisación bajo presión.</t>
   </si>
   <si>
+    <t xml:space="preserve">Media</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cada quien decide, o «el que grite más fuerte».</t>
   </si>
   <si>
@@ -1720,6 +1750,15 @@
     <t xml:space="preserve">Un desbalance explica los agotados sin más análisis.</t>
   </si>
   <si>
+    <t xml:space="preserve">En la zona de paqueteo trabajan 15 personas. FALTA el desglose entre alistamiento, rotulado y auditoría, y el dato de las demás zonas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recorrido 24/08</t>
+  </si>
+  <si>
     <t xml:space="preserve">Menos de 1 reabastecedor por cada 6 u 8 alistadores.</t>
   </si>
   <si>
@@ -1732,12 +1771,18 @@
     <t xml:space="preserve">Sin regla escrita, la secuencia depende del turno.</t>
   </si>
   <si>
+    <t xml:space="preserve">Hay una secuencia declarada de olas: primero nacional, después urbano y por último paqueteo. Las olas se envían según la programación y la capacidad disponible de alistamiento y despacho. La programación llega por correo con el rango de DT; Daniel toma el Excel, lo depura y monitorea si se despachó o no. FALTA: si la regla está escrita y publicada, o es criterio de Daniel.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Escribirla y publicarla en el piso. Es una acción de cero costo y efecto inmediato.</t>
   </si>
   <si>
     <t xml:space="preserve">Si no la conocen, alistan a ciegas contra el corte.</t>
   </si>
   <si>
+    <t xml:space="preserve">Paqueteo tiene corte hasta las 8:30–9:00 a.m. máximo. FALTA confirmar si alistamiento conoce la hora de cita de cada vehículo, o solo trabaja contra ese corte.</t>
+  </si>
+  <si>
     <t xml:space="preserve">No la conocen o llega tarde.</t>
   </si>
   <si>
@@ -1762,6 +1807,12 @@
     <t xml:space="preserve">Define si el pedido se arma de una vez o en pedazos que hay que consolidar después.</t>
   </si>
   <si>
+    <t xml:space="preserve">Separado y por canal. Paqueteo se alista por DT en las bandas y se agrupa por ola de trabajo; en los directos va un DT por ola de trabajo. Hay separación física de porcelana y grifería. Paso directo es caja completa. Marketplace agrupa Mercado Libre, Linio y Zona de Sueños, más grifería y porcelana. Directo son clientes grandes: un despacho por cliente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respondida</t>
+  </si>
+  <si>
     <t xml:space="preserve">Se alista separado y se junta en la puerta sin control.</t>
   </si>
   <si>
@@ -1774,6 +1825,9 @@
     <t xml:space="preserve">Revela el circuito real de la diferencia de inventario, que es donde se pierde el ERI.</t>
   </si>
   <si>
+    <t xml:space="preserve">Cuando hay producto mezclado entre EWM y WMS se generan novedades de inventario: se asigna una persona para hacer el traslado y la entrega baja a cero. Ocurre principalmente con Sodimac y Dina. También hay ajustes de inventario asociados a EAN 13 y EAN 14 cuando una misma caja sirve a varios clientes (ver nota a verificar al final de la hoja). FALTA: a quién se le informa formalmente y en cuánto tiempo se resuelve.</t>
+  </si>
+  <si>
     <t xml:space="preserve">El operario resuelve solo, toma de otra ubicación o simplemente no reporta.</t>
   </si>
   <si>
@@ -1789,6 +1843,9 @@
     <t xml:space="preserve">Un staging sin reglas de ubicación es donde se mezclan pedidos y rutas.</t>
   </si>
   <si>
+    <t xml:space="preserve">Daniel asigna la puerta a cada ola o DT, y la puerta se asigna de acuerdo con la zona de destino. FALTA: si hay marcación en piso y capacidad máxima definida por posición de staging.</t>
+  </si>
+  <si>
     <t xml:space="preserve">No hay marcación en piso ni posición asignada por ruta o vehículo.</t>
   </si>
   <si>
@@ -1801,6 +1858,9 @@
     <t xml:space="preserve">Es el último punto donde un error todavía no le costó al cliente.</t>
   </si>
   <si>
+    <t xml:space="preserve">En paqueteo hay auditoría de cajas en las bandas antes de agrupar por ola de trabajo. El propio CEDI reconoce que «toca mejorar el proceso en la puerta». FALTA: qué se verifica exactamente antes del cargue y si lo hace alguien distinto de quien alistó.</t>
+  </si>
+  <si>
     <t xml:space="preserve">El control es visual, o lo hace el mismo que alistó.</t>
   </si>
   <si>
@@ -1813,6 +1873,9 @@
     <t xml:space="preserve">Mezclar modos de transporte en el cargue produce despachos cruzados y devoluciones caras.</t>
   </si>
   <si>
+    <t xml:space="preserve">Paqueteo se gestiona todo en EWM, se cobra por peso-volumen y tiene corte hasta las 8:30–9:00 a.m. El rotulado y las guías los genera hoy el CEDI —antes los generaba la transportadora y se perdía mercancía— y se rotulan todas las cajas: ese es el cuello de botella declarado. Paso directo es caja completa. Directo son clientes grandes con un despacho por cliente. Una van de contenedor lleva mínimo 300 a 400 cajas.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Se distingue de memoria o por el color de la estiba, sin rótulo.</t>
   </si>
   <si>
@@ -1828,6 +1891,9 @@
     <t xml:space="preserve">PENDIENTE DE AJUSTAR: el mensaje original quedó cortado en la captura.</t>
   </si>
   <si>
+    <t xml:space="preserve">La programación llega por correo con el rango de DT y Daniel la administra en Excel: la depura y monitorea si se despachó o no. FALTA: confirmar la redacción original de la pregunta, que quedó cortada en la captura, y quién responde formalmente por el flujo centralizado.</t>
+  </si>
+  <si>
     <t xml:space="preserve">No hay un responsable claro del flujo centralizado.</t>
   </si>
   <si>
@@ -1852,6 +1918,9 @@
     <t xml:space="preserve">Muchas esperas son solo falta de aviso.</t>
   </si>
   <si>
+    <t xml:space="preserve">El monitoreo lo hace Daniel sobre el Excel de programación: revisa si se despachó o no. FALTA: si existe una señal formal de «listo para cargar» entre alistamiento y despacho, o despacho se entera al pasar.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nadie avisa: despacho lo descubre al pasar.</t>
   </si>
   <si>
@@ -1867,6 +1936,9 @@
     <t xml:space="preserve">Lo último en cargar debe ser lo primero en entregar. Casi nunca se pregunta.</t>
   </si>
   <si>
+    <t xml:space="preserve">Para Sodimac la carga se organiza por tienda. Sodimac se queja de forma recurrente de que el carro va desorganizado porque no está armado el combo; según Eli, organizarlo se paga aparte. El cargue puede durar todo el día. FALTA: si existe secuencia por orden inverso de entrega para el resto de rutas.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Se carga como vaya llegando.</t>
   </si>
   <si>
@@ -1891,6 +1963,9 @@
     <t xml:space="preserve">Sin este mapa, ningún dato que te entreguen después es interpretable.</t>
   </si>
   <si>
+    <t xml:space="preserve">Paqueteo se gestiona todo en EWM. Hay producto que queda mezclado entre EWM y WMS. FALTA: cuál de los dos corresponde al CD centralizado y cuál al descentralizado, y el alcance completo de cada uno por proceso.</t>
+  </si>
+  <si>
     <t xml:space="preserve">No lo saben con precisión, o cada área responde distinto.</t>
   </si>
   <si>
@@ -1900,6 +1975,9 @@
     <t xml:space="preserve">¿Cómo hacen la programación de olas en el CD descentralizado y cómo se conecta con el centralizado?</t>
   </si>
   <si>
+    <t xml:space="preserve">Las olas se envían según la programación y la capacidad de alistamiento y despacho, en orden: nacional, urbano y paqueteo. La programación llega por correo con el rango de DT y se administra en un Excel. FALTA: la parte de la conexión entre sistemas — la pregunta original quedó cortada.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Las olas se programan sin ver la carga del otro CD.</t>
   </si>
   <si>
@@ -1948,6 +2026,9 @@
     <t xml:space="preserve">Sin regla, cada quien decide y el inventario nunca converge.</t>
   </si>
   <si>
+    <t xml:space="preserve">Cuando hay producto mezclado se genera novedad de inventario, se asigna una persona para el traslado y la entrega baja a cero. Es el mecanismo de resolución, pero NO se identificó un sistema maestro declarado.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Depende de quién esté de turno.</t>
   </si>
   <si>
@@ -1972,10 +2053,13 @@
     <t xml:space="preserve">Los pedidos que cruzan los dos sistemas suelen ser los que más tiempo pierden.</t>
   </si>
   <si>
+    <t xml:space="preserve">Sí. Cuando el producto queda mezclado entre EWM y WMS hay que hacer un traslado manual con una persona asignada y la entrega baja a cero. Ocurre principalmente con Sodimac y Dina, y genera novedades de inventario.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sí, y la consolidación es manual.</t>
   </si>
   <si>
-    <t xml:space="preserve">Márcalos como «Ambos» en la hoja 6 y compara su ciclo contra el resto. Ahí queda cuantificado el costo de operar con dos sistemas.</t>
+    <t xml:space="preserve">Márcalos como «Ambos» en la hoja 6 y compara su ciclo contra el resto.</t>
   </si>
   <si>
     <t xml:space="preserve">¿Qué es lo que más tiempo le hace perder en el día?</t>
@@ -2032,6 +2116,12 @@
     <t xml:space="preserve">Mide si hay gestión o solo reacción.</t>
   </si>
   <si>
+    <t xml:space="preserve">El rotulado. Se rotulan todas las cajas y hoy el CEDI genera rótulos y guías —antes lo hacía la transportadora y se perdía mercancía—. Se suman: el proceso en la puerta, que reconocen que hay que mejorar; el alistamiento de paqueteo, que toma 5 horas; y el cargue, que puede durar todo el día. Restricción de sistema declarada: no deja generar la guía sin facturar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recorrido 24/08 · jefatura</t>
+  </si>
+  <si>
     <t xml:space="preserve">Responde «todo» o cambia de tema.</t>
   </si>
   <si>
@@ -2083,12 +2173,165 @@
     <t xml:space="preserve">La rotación alta explica errores sin que nadie tenga la culpa.</t>
   </si>
   <si>
+    <t xml:space="preserve">Baja</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rotación por encima del 30% anual.</t>
   </si>
   <si>
     <t xml:space="preserve">Con rotación alta siempre hay novatos. Reforzar certificación antes de operar solo.</t>
   </si>
   <si>
+    <t xml:space="preserve">  NOTAS DEL RECORRIDO — HECHOS QUE NO RESPONDEN NINGUNA PREGUNTA DEL BANCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hecho registrado en el recorrido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qué abre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paqueteo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte hasta las 8:30 – 9:00 a.m. máximo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Lo fija la transportadora o el CEDI? ¿Qué pasa con lo que entra después de esa hora?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 horas para alistar paqueteo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Contra qué volumen? ¿Cabe dentro del corte de las 9:00 a.m. o arranca del día anterior?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En la zona de paqueteo trabajan 15 personas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuántas alistan, cuántas rotulan y cuántas auditan? El rotulado es el cuello declarado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La transportadora de paqueteo cobra por peso-volumen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Se optimiza el empaque para reducir el volumen facturado? Puede ser ahorro directo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rotulado y guías</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antes la transportadora generaba guía y rótulo y se perdía mercancía. Hoy los genera el CEDI y se rotulan todas las cajas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El cambio resolvió la pérdida pero creó el cuello de botella. ¿Cuánto tiempo agregó y cuánta pérdida evitó? Con las dos cifras se decide si se automatiza.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restricción de sistema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No deja generar la guía sin facturar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto retrasa el despacho? ¿Es configurable o es política? Es la respuesta parcial a si algo en el sistema restringe entregar más rápido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El cargue puede durar todo el día.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuántos muelles, cuántas personas y cuántos vehículos? Se cruza con la hoja 8.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una van de contenedor lleva mínimo 300 a 400 cajas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuántas vans por día? Da la base para calcular productividad de cargue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketplace agrupa Mercado Libre, Linio y Zona de Sueños, más grifería y porcelana.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Volumen y ciclo propio de cada canal? Los marketplace suelen tener promesa de entrega más corta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directo son clientes grandes: un despacho por cliente. Paso directo es caja completa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué porcentaje del volumen total va por cada canal y cuál consume más recurso?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sodimac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se queja de forma recurrente de que el carro va desorganizado porque no está armado el combo. Se organiza por tienda. Según Eli, organizarlo se paga aparte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Está costeado y cobrado ese servicio? ¿Cuánto cuesta la queja frente a lo que cuesta organizarlo?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inventario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Ajustes de inventario Ean 13 y Ean 14, caja para varios clientes, las quintas termina 5 rotura».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERIFICAR REDACCIÓN — la nota quedó incompleta. Se transcribe literal, sin interpretar. Confirmar antes de usarla como hallazgo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acción pendiente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Validar para consolidar por zona, sector».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Quién lo valida y para cuándo? Si se confirma, pasa a la hoja 11 con dueño y fecha.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  PREGUNTAS ABIERTAS PARA LA REUNIÓN — LAS QUE QUEDASTE DEBIENDO EN EL RECORRIDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De dónde sale / por qué importa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Hay algo en el sistema que restrinja entregar más rápido?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ya tienes una respuesta parcial: no deja generar la guía sin facturar. Falta saber si hay más restricciones y si son configurables.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Por qué a un mismo cliente se le envían varios DT en la programación el mismo día?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si un cliente recibe varios DT el mismo día, se multiplican alistamientos, rótulos y guías para un solo destino. Puede ser consolidable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Confirmar el circuito del Excel: Daniel lo recibe, lo depura y monitorea si se despachó o no?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es el control real de la programación. Si depende de una sola persona y de un archivo, es un punto único de falla.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuál de los dos sistemas, EWM o WMS, corresponde al CD centralizado y cuál al descentralizado?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sin esto, ningún dato que te entreguen después es interpretable por sistema.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuántos casos de producto mezclado entre EWM y WMS ocurren por semana?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sabes que pasa con Sodimac y Dina y que obliga a traslado manual. Falta la frecuencia para dimensionar el costo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CÓMO SE USA EN LA REUNIÓN — Ordena por Prioridad y trabaja solo las que digan Pendiente; las Parciales ya traen escrito qué pedazo falta, así que ahí preguntas una sola cosa. Dos advertencias: el rotulado como cuello de botella lo declaró la jefatura, no un operario, por eso las preguntas del grupo «Operario» siguen pendientes y hay que hacerlas en piso; y la nota de EAN 13 y EAN 14 quedó incompleta, así que confírmala antes de convertirla en hallazgo.</t>
+  </si>
+  <si>
     <t xml:space="preserve">10 · SOLICITUD DE INFORMACIÓN</t>
   </si>
   <si>
@@ -2741,9 +2984,6 @@
   </si>
   <si>
     <t xml:space="preserve">Cada repetición es tiempo perdido y un punto de error.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paqueteo</t>
   </si>
   <si>
     <t xml:space="preserve">Envío de pocas unidades por transportadora de mensajería, sin vehículo dedicado.</t>
@@ -2812,7 +3052,7 @@
     <numFmt numFmtId="171" formatCode="\+0.0%;\-0.0%;0.0%"/>
     <numFmt numFmtId="172" formatCode="hh:mm"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3050,6 +3290,53 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF0A3A5C"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF17683F"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF8A5500"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF9E2420"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF00329B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9.5"/>
+      <color rgb="FF1A1F26"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="9"/>
       <color rgb="FF9E2420"/>
       <name val="Arial"/>
@@ -3065,7 +3352,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3124,6 +3411,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF9E2420"/>
         <bgColor rgb="FF993366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF0D8"/>
+        <bgColor rgb="FFFFF6D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -3219,7 +3512,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="99">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3517,14 +3810,58 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="32" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="33" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="34" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="35" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="35" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3532,7 +3869,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3544,7 +3881,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3556,7 +3893,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="33" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="39" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3564,7 +3901,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="33" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="39" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3581,7 +3918,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="13">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -3716,6 +4053,51 @@
         <family val="0"/>
         <color rgb="FF9E2420"/>
         <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF9E4E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF17683F"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE1F0E8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF8A5500"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFBF0D8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF9E2420"/>
+        <sz val="9"/>
       </font>
       <fill>
         <patternFill>
@@ -5673,14 +6055,18 @@
     <tabColor rgb="FF1B7A4C"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5692,6 +6078,9 @@
       <c r="D1" s="19"/>
       <c r="E1" s="19"/>
       <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
@@ -5702,6 +6091,9 @@
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
       <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
@@ -5712,6 +6104,9 @@
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="35" t="s">
@@ -5724,6 +6119,9 @@
       <c r="D5" s="36"/>
       <c r="E5" s="36"/>
       <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="35" t="s">
@@ -5736,6 +6134,9 @@
       <c r="D6" s="36"/>
       <c r="E6" s="36"/>
       <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="35" t="s">
@@ -5748,8 +6149,11 @@
       <c r="D7" s="36"/>
       <c r="E7" s="36"/>
       <c r="F7" s="36"/>
-    </row>
-    <row r="8" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+    </row>
+    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
         <v>190</v>
       </c>
@@ -5760,729 +6164,1610 @@
       <c r="D8" s="36"/>
       <c r="E8" s="36"/>
       <c r="F8" s="36"/>
-    </row>
-    <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="73" t="s">
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+    </row>
+    <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="B9" s="36" t="s">
         <v>522</v>
       </c>
-      <c r="B9" s="73"/>
-      <c r="C9" s="73"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-    </row>
-    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+    </row>
+    <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="73" t="s">
         <v>523</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="73"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73"/>
+    </row>
+    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
         <v>524</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="74" t="s">
+      <c r="B11" s="8"/>
+      <c r="C11" s="8" t="s">
         <v>525</v>
       </c>
-      <c r="B11" s="75" t="s">
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="74" t="s">
         <v>526</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="74" t="s">
+      <c r="B12" s="74"/>
+      <c r="C12" s="75" t="s">
         <v>527</v>
       </c>
-      <c r="B12" s="75" t="s">
+      <c r="D12" s="75"/>
+      <c r="E12" s="75"/>
+    </row>
+    <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="74" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="74" t="s">
+      <c r="B13" s="74"/>
+      <c r="C13" s="75" t="s">
         <v>529</v>
       </c>
-      <c r="B13" s="75" t="s">
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
+    </row>
+    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="74" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="74" t="s">
+      <c r="B14" s="74"/>
+      <c r="C14" s="75" t="s">
         <v>531</v>
       </c>
-      <c r="B14" s="75" t="s">
+      <c r="D14" s="75"/>
+      <c r="E14" s="75"/>
+    </row>
+    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="74" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="74" t="s">
+      <c r="B15" s="74"/>
+      <c r="C15" s="75" t="s">
         <v>533</v>
       </c>
-      <c r="B15" s="75" t="s">
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
+    </row>
+    <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="74" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="74" t="s">
+      <c r="B16" s="74"/>
+      <c r="C16" s="75" t="s">
         <v>535</v>
       </c>
-      <c r="B16" s="75" t="s">
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
+    </row>
+    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="74" t="s">
         <v>536</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="B17" s="74"/>
+      <c r="C17" s="75" t="s">
         <v>537</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
+      <c r="D17" s="75"/>
+      <c r="E17" s="75"/>
+    </row>
+    <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
         <v>539</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="B20" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="C20" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="76" t="n">
+        <f aca="false">COUNTA($B$25:$B$58)</f>
+        <v>34</v>
+      </c>
+      <c r="B21" s="77" t="n">
+        <f aca="false">COUNTIF($E$25:$E$58,"Respondida")</f>
+        <v>4</v>
+      </c>
+      <c r="C21" s="78" t="n">
+        <f aca="false">COUNTIF($E$25:$E$58,"Parcial")</f>
+        <v>12</v>
+      </c>
+      <c r="D21" s="79" t="n">
+        <f aca="false">COUNTIF($E$25:$E$58,"Pendiente")</f>
+        <v>18</v>
+      </c>
+      <c r="E21" s="80" t="n">
+        <f aca="false">IF($A$21=0,"",$D$21/$A$21)</f>
+        <v>0.529411764705882</v>
+      </c>
+      <c r="F21" s="69" t="s">
+        <v>543</v>
+      </c>
+      <c r="G21" s="69"/>
+      <c r="H21" s="69"/>
+      <c r="I21" s="69"/>
+    </row>
+    <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+    </row>
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E24" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="H24" s="8" t="s">
         <v>449</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
-        <v>542</v>
-      </c>
-      <c r="B20" s="76" t="s">
-        <v>543</v>
-      </c>
-      <c r="C20" s="32" t="s">
-        <v>544</v>
-      </c>
-      <c r="D20" s="34"/>
-      <c r="E20" s="70" t="s">
-        <v>545</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
-        <v>542</v>
-      </c>
-      <c r="B21" s="76" t="s">
-        <v>547</v>
-      </c>
-      <c r="C21" s="32" t="s">
-        <v>548</v>
-      </c>
-      <c r="D21" s="34"/>
-      <c r="E21" s="70" t="s">
+      <c r="I24" s="8" t="s">
         <v>549</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="s">
-        <v>542</v>
-      </c>
-      <c r="B22" s="76" t="s">
-        <v>551</v>
-      </c>
-      <c r="C22" s="32" t="s">
-        <v>552</v>
-      </c>
-      <c r="D22" s="34"/>
-      <c r="E22" s="70" t="s">
-        <v>553</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
-        <v>542</v>
-      </c>
-      <c r="B23" s="76" t="s">
-        <v>327</v>
-      </c>
-      <c r="C23" s="32" t="s">
-        <v>555</v>
-      </c>
-      <c r="D23" s="34"/>
-      <c r="E23" s="70" t="s">
-        <v>556</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
-        <v>558</v>
-      </c>
-      <c r="B24" s="76" t="s">
-        <v>450</v>
-      </c>
-      <c r="C24" s="32" t="s">
-        <v>559</v>
-      </c>
-      <c r="D24" s="34"/>
-      <c r="E24" s="70" t="s">
-        <v>451</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>558</v>
-      </c>
-      <c r="B25" s="76" t="s">
-        <v>455</v>
+        <v>550</v>
+      </c>
+      <c r="B25" s="81" t="s">
+        <v>551</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>561</v>
-      </c>
-      <c r="D25" s="34"/>
-      <c r="E25" s="70" t="s">
-        <v>562</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>563</v>
+        <v>552</v>
+      </c>
+      <c r="D25" s="82"/>
+      <c r="E25" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="F25" s="84"/>
+      <c r="G25" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H25" s="70" t="s">
+        <v>554</v>
+      </c>
+      <c r="I25" s="26" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="B26" s="81" t="s">
+        <v>556</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>557</v>
+      </c>
+      <c r="D26" s="82"/>
+      <c r="E26" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="F26" s="84"/>
+      <c r="G26" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H26" s="70" t="s">
         <v>558</v>
       </c>
-      <c r="B26" s="76" t="s">
-        <v>440</v>
-      </c>
-      <c r="C26" s="32" t="s">
-        <v>564</v>
-      </c>
-      <c r="D26" s="34"/>
-      <c r="E26" s="70" t="s">
-        <v>565</v>
-      </c>
-      <c r="F26" s="26" t="s">
-        <v>566</v>
+      <c r="I26" s="26" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="B27" s="81" t="s">
+        <v>560</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>561</v>
+      </c>
+      <c r="D27" s="82"/>
+      <c r="E27" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="F27" s="84"/>
+      <c r="G27" s="83" t="s">
+        <v>562</v>
+      </c>
+      <c r="H27" s="70" t="s">
+        <v>563</v>
+      </c>
+      <c r="I27" s="26" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="B28" s="81" t="s">
+        <v>327</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>565</v>
+      </c>
+      <c r="D28" s="82" t="s">
+        <v>566</v>
+      </c>
+      <c r="E28" s="83" t="s">
         <v>567</v>
       </c>
-      <c r="B27" s="76" t="s">
+      <c r="F28" s="84" t="s">
         <v>568</v>
       </c>
-      <c r="C27" s="32" t="s">
+      <c r="G28" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H28" s="70" t="s">
         <v>569</v>
       </c>
-      <c r="D27" s="34"/>
-      <c r="E27" s="70" t="s">
+      <c r="I28" s="26" t="s">
         <v>570</v>
       </c>
-      <c r="F27" s="26" t="s">
+    </row>
+    <row r="29" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9" t="s">
+      <c r="B29" s="81" t="s">
+        <v>450</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>572</v>
+      </c>
+      <c r="D29" s="82" t="s">
+        <v>573</v>
+      </c>
+      <c r="E29" s="83" t="s">
         <v>567</v>
       </c>
-      <c r="B28" s="76" t="s">
-        <v>572</v>
-      </c>
-      <c r="C28" s="32" t="s">
-        <v>573</v>
-      </c>
-      <c r="D28" s="34"/>
-      <c r="E28" s="70" t="s">
+      <c r="F29" s="84" t="s">
+        <v>568</v>
+      </c>
+      <c r="G29" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H29" s="70" t="s">
+        <v>451</v>
+      </c>
+      <c r="I29" s="26" t="s">
         <v>574</v>
       </c>
-      <c r="F28" s="26" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="B30" s="81" t="s">
+        <v>455</v>
+      </c>
+      <c r="C30" s="32" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9" t="s">
+      <c r="D30" s="82" t="s">
         <v>576</v>
       </c>
-      <c r="B29" s="76" t="s">
+      <c r="E30" s="83" t="s">
+        <v>567</v>
+      </c>
+      <c r="F30" s="84" t="s">
+        <v>568</v>
+      </c>
+      <c r="G30" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H30" s="70" t="s">
         <v>577</v>
       </c>
-      <c r="C29" s="32" t="s">
+      <c r="I30" s="26" t="s">
         <v>578</v>
-      </c>
-      <c r="D29" s="34"/>
-      <c r="E29" s="70" t="s">
-        <v>579</v>
-      </c>
-      <c r="F29" s="26" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9" t="s">
-        <v>576</v>
-      </c>
-      <c r="B30" s="76" t="s">
-        <v>581</v>
-      </c>
-      <c r="C30" s="32" t="s">
-        <v>582</v>
-      </c>
-      <c r="D30" s="34"/>
-      <c r="E30" s="70" t="s">
-        <v>583</v>
-      </c>
-      <c r="F30" s="26" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>576</v>
-      </c>
-      <c r="B31" s="76" t="s">
+        <v>571</v>
+      </c>
+      <c r="B31" s="81" t="s">
+        <v>440</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>579</v>
+      </c>
+      <c r="D31" s="82"/>
+      <c r="E31" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="F31" s="84"/>
+      <c r="G31" s="83" t="s">
+        <v>562</v>
+      </c>
+      <c r="H31" s="70" t="s">
+        <v>580</v>
+      </c>
+      <c r="I31" s="26" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="B32" s="81" t="s">
+        <v>583</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>584</v>
+      </c>
+      <c r="D32" s="82" t="s">
         <v>585</v>
       </c>
-      <c r="C31" s="32" t="s">
+      <c r="E32" s="83" t="s">
         <v>586</v>
       </c>
-      <c r="D31" s="34"/>
-      <c r="E31" s="70" t="s">
+      <c r="F32" s="84" t="s">
+        <v>568</v>
+      </c>
+      <c r="G32" s="83" t="s">
+        <v>562</v>
+      </c>
+      <c r="H32" s="70" t="s">
         <v>587</v>
       </c>
-      <c r="F31" s="26" t="s">
+      <c r="I32" s="26" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9" t="s">
+    <row r="33" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="B33" s="81" t="s">
         <v>589</v>
       </c>
-      <c r="B32" s="76" t="s">
+      <c r="C33" s="32" t="s">
         <v>590</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="D33" s="82" t="s">
         <v>591</v>
       </c>
-      <c r="D32" s="34"/>
-      <c r="E32" s="70" t="s">
+      <c r="E33" s="83" t="s">
+        <v>567</v>
+      </c>
+      <c r="F33" s="84" t="s">
+        <v>568</v>
+      </c>
+      <c r="G33" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H33" s="70" t="s">
         <v>592</v>
       </c>
-      <c r="F32" s="26" t="s">
+      <c r="I33" s="26" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9" t="s">
-        <v>594</v>
-      </c>
-      <c r="B33" s="76" t="s">
-        <v>595</v>
-      </c>
-      <c r="C33" s="32" t="s">
-        <v>596</v>
-      </c>
-      <c r="D33" s="34"/>
-      <c r="E33" s="70" t="s">
-        <v>597</v>
-      </c>
-      <c r="F33" s="26" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
         <v>594</v>
       </c>
-      <c r="B34" s="76" t="s">
-        <v>384</v>
+      <c r="B34" s="81" t="s">
+        <v>595</v>
       </c>
       <c r="C34" s="32" t="s">
+        <v>596</v>
+      </c>
+      <c r="D34" s="82" t="s">
+        <v>597</v>
+      </c>
+      <c r="E34" s="83" t="s">
+        <v>567</v>
+      </c>
+      <c r="F34" s="84" t="s">
+        <v>568</v>
+      </c>
+      <c r="G34" s="83" t="s">
+        <v>562</v>
+      </c>
+      <c r="H34" s="70" t="s">
+        <v>598</v>
+      </c>
+      <c r="I34" s="26" t="s">
         <v>599</v>
       </c>
-      <c r="D34" s="34"/>
-      <c r="E34" s="70" t="s">
+    </row>
+    <row r="35" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="B35" s="81" t="s">
         <v>600</v>
       </c>
-      <c r="F34" s="26" t="s">
+      <c r="C35" s="32" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9" t="s">
+      <c r="D35" s="82" t="s">
         <v>602</v>
       </c>
-      <c r="B35" s="76" t="s">
+      <c r="E35" s="83" t="s">
+        <v>567</v>
+      </c>
+      <c r="F35" s="84" t="s">
+        <v>568</v>
+      </c>
+      <c r="G35" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H35" s="70" t="s">
         <v>603</v>
       </c>
-      <c r="C35" s="32" t="s">
+      <c r="I35" s="26" t="s">
         <v>604</v>
       </c>
-      <c r="D35" s="34"/>
-      <c r="E35" s="70" t="s">
+    </row>
+    <row r="36" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="B36" s="81" t="s">
         <v>605</v>
       </c>
-      <c r="F35" s="26" t="s">
+      <c r="C36" s="32" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9" t="s">
-        <v>602</v>
-      </c>
-      <c r="B36" s="76" t="s">
-        <v>491</v>
-      </c>
-      <c r="C36" s="32" t="s">
+      <c r="D36" s="82" t="s">
         <v>607</v>
       </c>
-      <c r="D36" s="34"/>
-      <c r="E36" s="70" t="s">
+      <c r="E36" s="83" t="s">
+        <v>586</v>
+      </c>
+      <c r="F36" s="84" t="s">
+        <v>568</v>
+      </c>
+      <c r="G36" s="83" t="s">
+        <v>562</v>
+      </c>
+      <c r="H36" s="70" t="s">
         <v>608</v>
       </c>
-      <c r="F36" s="26" t="s">
+      <c r="I36" s="26" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
         <v>610</v>
       </c>
-      <c r="B37" s="76" t="s">
+      <c r="B37" s="81" t="s">
         <v>611</v>
       </c>
       <c r="C37" s="32" t="s">
         <v>612</v>
       </c>
-      <c r="D37" s="34"/>
-      <c r="E37" s="70" t="s">
+      <c r="D37" s="82" t="s">
         <v>613</v>
       </c>
-      <c r="F37" s="26" t="s">
+      <c r="E37" s="83" t="s">
+        <v>567</v>
+      </c>
+      <c r="F37" s="84" t="s">
+        <v>568</v>
+      </c>
+      <c r="G37" s="83" t="s">
+        <v>562</v>
+      </c>
+      <c r="H37" s="70" t="s">
         <v>614</v>
+      </c>
+      <c r="I37" s="26" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>610</v>
-      </c>
-      <c r="B38" s="76" t="s">
-        <v>615</v>
+        <v>616</v>
+      </c>
+      <c r="B38" s="81" t="s">
+        <v>617</v>
       </c>
       <c r="C38" s="32" t="s">
-        <v>591</v>
-      </c>
-      <c r="D38" s="34"/>
-      <c r="E38" s="70" t="s">
+        <v>618</v>
+      </c>
+      <c r="D38" s="82"/>
+      <c r="E38" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="F38" s="84"/>
+      <c r="G38" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H38" s="70" t="s">
+        <v>619</v>
+      </c>
+      <c r="I38" s="26" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="9" t="s">
         <v>616</v>
       </c>
-      <c r="F38" s="26" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="9" t="s">
-        <v>610</v>
-      </c>
-      <c r="B39" s="76" t="s">
-        <v>618</v>
+      <c r="B39" s="81" t="s">
+        <v>384</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>619</v>
-      </c>
-      <c r="D39" s="34"/>
-      <c r="E39" s="70" t="s">
-        <v>620</v>
-      </c>
-      <c r="F39" s="26" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D39" s="82" t="s">
+        <v>622</v>
+      </c>
+      <c r="E39" s="83" t="s">
+        <v>567</v>
+      </c>
+      <c r="F39" s="84" t="s">
+        <v>568</v>
+      </c>
+      <c r="G39" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H39" s="70" t="s">
+        <v>623</v>
+      </c>
+      <c r="I39" s="26" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
-        <v>610</v>
-      </c>
-      <c r="B40" s="76" t="s">
-        <v>622</v>
+        <v>625</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>626</v>
       </c>
       <c r="C40" s="32" t="s">
-        <v>623</v>
-      </c>
-      <c r="D40" s="34"/>
-      <c r="E40" s="70" t="s">
-        <v>624</v>
-      </c>
-      <c r="F40" s="26" t="s">
-        <v>625</v>
+        <v>627</v>
+      </c>
+      <c r="D40" s="82" t="s">
+        <v>628</v>
+      </c>
+      <c r="E40" s="83" t="s">
+        <v>567</v>
+      </c>
+      <c r="F40" s="84" t="s">
+        <v>568</v>
+      </c>
+      <c r="G40" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H40" s="70" t="s">
+        <v>629</v>
+      </c>
+      <c r="I40" s="26" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>610</v>
-      </c>
-      <c r="B41" s="76" t="s">
-        <v>626</v>
+        <v>625</v>
+      </c>
+      <c r="B41" s="81" t="s">
+        <v>491</v>
       </c>
       <c r="C41" s="32" t="s">
-        <v>627</v>
-      </c>
-      <c r="D41" s="34"/>
-      <c r="E41" s="70" t="s">
-        <v>628</v>
-      </c>
-      <c r="F41" s="26" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>631</v>
+      </c>
+      <c r="D41" s="82"/>
+      <c r="E41" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="F41" s="84"/>
+      <c r="G41" s="83" t="s">
+        <v>562</v>
+      </c>
+      <c r="H41" s="70" t="s">
+        <v>632</v>
+      </c>
+      <c r="I41" s="26" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>610</v>
-      </c>
-      <c r="B42" s="76" t="s">
-        <v>630</v>
+        <v>634</v>
+      </c>
+      <c r="B42" s="81" t="s">
+        <v>635</v>
       </c>
       <c r="C42" s="32" t="s">
-        <v>631</v>
-      </c>
-      <c r="D42" s="34"/>
-      <c r="E42" s="70" t="s">
-        <v>632</v>
-      </c>
-      <c r="F42" s="26" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>636</v>
+      </c>
+      <c r="D42" s="82" t="s">
+        <v>637</v>
+      </c>
+      <c r="E42" s="83" t="s">
+        <v>567</v>
+      </c>
+      <c r="F42" s="84" t="s">
+        <v>568</v>
+      </c>
+      <c r="G42" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H42" s="70" t="s">
+        <v>638</v>
+      </c>
+      <c r="I42" s="26" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>610</v>
-      </c>
-      <c r="B43" s="76" t="s">
         <v>634</v>
       </c>
+      <c r="B43" s="81" t="s">
+        <v>640</v>
+      </c>
       <c r="C43" s="32" t="s">
-        <v>635</v>
-      </c>
-      <c r="D43" s="34"/>
-      <c r="E43" s="70" t="s">
-        <v>636</v>
-      </c>
-      <c r="F43" s="26" t="s">
-        <v>637</v>
+        <v>612</v>
+      </c>
+      <c r="D43" s="82" t="s">
+        <v>641</v>
+      </c>
+      <c r="E43" s="83" t="s">
+        <v>567</v>
+      </c>
+      <c r="F43" s="84" t="s">
+        <v>568</v>
+      </c>
+      <c r="G43" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H43" s="70" t="s">
+        <v>642</v>
+      </c>
+      <c r="I43" s="26" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>610</v>
-      </c>
-      <c r="B44" s="76" t="s">
-        <v>638</v>
+        <v>634</v>
+      </c>
+      <c r="B44" s="81" t="s">
+        <v>644</v>
       </c>
       <c r="C44" s="32" t="s">
-        <v>639</v>
-      </c>
-      <c r="D44" s="34"/>
-      <c r="E44" s="70" t="s">
-        <v>640</v>
-      </c>
-      <c r="F44" s="26" t="s">
-        <v>641</v>
+        <v>645</v>
+      </c>
+      <c r="D44" s="82"/>
+      <c r="E44" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="F44" s="84"/>
+      <c r="G44" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H44" s="70" t="s">
+        <v>646</v>
+      </c>
+      <c r="I44" s="26" t="s">
+        <v>647</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="B45" s="76" t="s">
-        <v>642</v>
+        <v>634</v>
+      </c>
+      <c r="B45" s="81" t="s">
+        <v>648</v>
       </c>
       <c r="C45" s="32" t="s">
-        <v>643</v>
-      </c>
-      <c r="D45" s="34"/>
-      <c r="E45" s="70" t="s">
-        <v>644</v>
-      </c>
-      <c r="F45" s="26" t="s">
-        <v>645</v>
+        <v>649</v>
+      </c>
+      <c r="D45" s="82"/>
+      <c r="E45" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="F45" s="84"/>
+      <c r="G45" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H45" s="70" t="s">
+        <v>650</v>
+      </c>
+      <c r="I45" s="26" t="s">
+        <v>651</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="B46" s="76" t="s">
-        <v>646</v>
+        <v>634</v>
+      </c>
+      <c r="B46" s="81" t="s">
+        <v>652</v>
       </c>
       <c r="C46" s="32" t="s">
-        <v>647</v>
-      </c>
-      <c r="D46" s="34"/>
-      <c r="E46" s="70" t="s">
-        <v>648</v>
-      </c>
-      <c r="F46" s="26" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>653</v>
+      </c>
+      <c r="D46" s="82"/>
+      <c r="E46" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="F46" s="84"/>
+      <c r="G46" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H46" s="70" t="s">
+        <v>654</v>
+      </c>
+      <c r="I46" s="26" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="B47" s="76" t="s">
-        <v>650</v>
+        <v>634</v>
+      </c>
+      <c r="B47" s="81" t="s">
+        <v>656</v>
       </c>
       <c r="C47" s="32" t="s">
-        <v>651</v>
-      </c>
-      <c r="D47" s="34"/>
-      <c r="E47" s="70" t="s">
-        <v>652</v>
-      </c>
-      <c r="F47" s="26" t="s">
-        <v>653</v>
+        <v>657</v>
+      </c>
+      <c r="D47" s="82" t="s">
+        <v>658</v>
+      </c>
+      <c r="E47" s="83" t="s">
+        <v>567</v>
+      </c>
+      <c r="F47" s="84" t="s">
+        <v>568</v>
+      </c>
+      <c r="G47" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H47" s="70" t="s">
+        <v>659</v>
+      </c>
+      <c r="I47" s="26" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="B48" s="76" t="s">
-        <v>654</v>
+        <v>634</v>
+      </c>
+      <c r="B48" s="81" t="s">
+        <v>661</v>
       </c>
       <c r="C48" s="32" t="s">
-        <v>655</v>
-      </c>
-      <c r="D48" s="34"/>
-      <c r="E48" s="70" t="s">
-        <v>656</v>
-      </c>
-      <c r="F48" s="26" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>662</v>
+      </c>
+      <c r="D48" s="82"/>
+      <c r="E48" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="F48" s="84"/>
+      <c r="G48" s="83" t="s">
+        <v>562</v>
+      </c>
+      <c r="H48" s="70" t="s">
+        <v>663</v>
+      </c>
+      <c r="I48" s="26" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B49" s="76" t="s">
-        <v>658</v>
+        <v>634</v>
+      </c>
+      <c r="B49" s="81" t="s">
+        <v>665</v>
       </c>
       <c r="C49" s="32" t="s">
-        <v>659</v>
-      </c>
-      <c r="D49" s="34"/>
-      <c r="E49" s="70" t="s">
-        <v>660</v>
-      </c>
-      <c r="F49" s="26" t="s">
-        <v>661</v>
+        <v>666</v>
+      </c>
+      <c r="D49" s="82" t="s">
+        <v>667</v>
+      </c>
+      <c r="E49" s="83" t="s">
+        <v>586</v>
+      </c>
+      <c r="F49" s="84" t="s">
+        <v>568</v>
+      </c>
+      <c r="G49" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H49" s="70" t="s">
+        <v>668</v>
+      </c>
+      <c r="I49" s="26" t="s">
+        <v>669</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50" s="76" t="s">
-        <v>662</v>
+        <v>256</v>
+      </c>
+      <c r="B50" s="81" t="s">
+        <v>670</v>
       </c>
       <c r="C50" s="32" t="s">
-        <v>663</v>
-      </c>
-      <c r="D50" s="34"/>
-      <c r="E50" s="70" t="s">
-        <v>664</v>
-      </c>
-      <c r="F50" s="26" t="s">
-        <v>665</v>
+        <v>671</v>
+      </c>
+      <c r="D50" s="82"/>
+      <c r="E50" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="F50" s="84"/>
+      <c r="G50" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H50" s="70" t="s">
+        <v>672</v>
+      </c>
+      <c r="I50" s="26" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B51" s="76" t="s">
-        <v>666</v>
+        <v>256</v>
+      </c>
+      <c r="B51" s="81" t="s">
+        <v>674</v>
       </c>
       <c r="C51" s="32" t="s">
-        <v>667</v>
-      </c>
-      <c r="D51" s="34"/>
-      <c r="E51" s="70" t="s">
-        <v>668</v>
-      </c>
-      <c r="F51" s="26" t="s">
-        <v>669</v>
+        <v>675</v>
+      </c>
+      <c r="D51" s="82"/>
+      <c r="E51" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="F51" s="84"/>
+      <c r="G51" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H51" s="70" t="s">
+        <v>676</v>
+      </c>
+      <c r="I51" s="26" t="s">
+        <v>677</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="B52" s="76" t="s">
-        <v>670</v>
+        <v>256</v>
+      </c>
+      <c r="B52" s="81" t="s">
+        <v>678</v>
       </c>
       <c r="C52" s="32" t="s">
-        <v>671</v>
-      </c>
-      <c r="D52" s="34"/>
-      <c r="E52" s="70" t="s">
-        <v>672</v>
-      </c>
-      <c r="F52" s="26" t="s">
-        <v>673</v>
+        <v>679</v>
+      </c>
+      <c r="D52" s="82"/>
+      <c r="E52" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="F52" s="84"/>
+      <c r="G52" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H52" s="70" t="s">
+        <v>680</v>
+      </c>
+      <c r="I52" s="26" t="s">
+        <v>681</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="B53" s="76" t="s">
-        <v>675</v>
+        <v>256</v>
+      </c>
+      <c r="B53" s="81" t="s">
+        <v>682</v>
       </c>
       <c r="C53" s="32" t="s">
-        <v>676</v>
-      </c>
-      <c r="D53" s="34"/>
-      <c r="E53" s="70" t="s">
-        <v>677</v>
-      </c>
-      <c r="F53" s="26" t="s">
-        <v>678</v>
-      </c>
+        <v>683</v>
+      </c>
+      <c r="D53" s="82"/>
+      <c r="E53" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="F53" s="84"/>
+      <c r="G53" s="83" t="s">
+        <v>562</v>
+      </c>
+      <c r="H53" s="70" t="s">
+        <v>684</v>
+      </c>
+      <c r="I53" s="26" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" s="81" t="s">
+        <v>686</v>
+      </c>
+      <c r="C54" s="32" t="s">
+        <v>687</v>
+      </c>
+      <c r="D54" s="82" t="s">
+        <v>688</v>
+      </c>
+      <c r="E54" s="83" t="s">
+        <v>586</v>
+      </c>
+      <c r="F54" s="84" t="s">
+        <v>689</v>
+      </c>
+      <c r="G54" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H54" s="70" t="s">
+        <v>690</v>
+      </c>
+      <c r="I54" s="26" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="81" t="s">
+        <v>692</v>
+      </c>
+      <c r="C55" s="32" t="s">
+        <v>693</v>
+      </c>
+      <c r="D55" s="82"/>
+      <c r="E55" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="F55" s="84"/>
+      <c r="G55" s="83" t="s">
+        <v>407</v>
+      </c>
+      <c r="H55" s="70" t="s">
+        <v>694</v>
+      </c>
+      <c r="I55" s="26" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" s="81" t="s">
+        <v>696</v>
+      </c>
+      <c r="C56" s="32" t="s">
+        <v>697</v>
+      </c>
+      <c r="D56" s="82"/>
+      <c r="E56" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="F56" s="84"/>
+      <c r="G56" s="83" t="s">
+        <v>562</v>
+      </c>
+      <c r="H56" s="70" t="s">
+        <v>698</v>
+      </c>
+      <c r="I56" s="26" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="B57" s="81" t="s">
+        <v>700</v>
+      </c>
+      <c r="C57" s="32" t="s">
+        <v>701</v>
+      </c>
+      <c r="D57" s="82"/>
+      <c r="E57" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="F57" s="84"/>
+      <c r="G57" s="83" t="s">
+        <v>562</v>
+      </c>
+      <c r="H57" s="70" t="s">
+        <v>702</v>
+      </c>
+      <c r="I57" s="26" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="B58" s="81" t="s">
+        <v>705</v>
+      </c>
+      <c r="C58" s="32" t="s">
+        <v>706</v>
+      </c>
+      <c r="D58" s="82"/>
+      <c r="E58" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="F58" s="84"/>
+      <c r="G58" s="83" t="s">
+        <v>707</v>
+      </c>
+      <c r="H58" s="70" t="s">
+        <v>708</v>
+      </c>
+      <c r="I58" s="26" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="7" t="s">
+        <v>710</v>
+      </c>
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
+    </row>
+    <row r="61" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="C61" s="8"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="8"/>
+    </row>
+    <row r="62" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>715</v>
+      </c>
+      <c r="C62" s="10"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="32" t="s">
+        <v>716</v>
+      </c>
+      <c r="G62" s="32"/>
+      <c r="H62" s="32"/>
+      <c r="I62" s="32"/>
+    </row>
+    <row r="63" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>717</v>
+      </c>
+      <c r="C63" s="10"/>
+      <c r="D63" s="10"/>
+      <c r="E63" s="10"/>
+      <c r="F63" s="32" t="s">
+        <v>718</v>
+      </c>
+      <c r="G63" s="32"/>
+      <c r="H63" s="32"/>
+      <c r="I63" s="32"/>
+    </row>
+    <row r="64" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>719</v>
+      </c>
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="10"/>
+      <c r="F64" s="32" t="s">
+        <v>720</v>
+      </c>
+      <c r="G64" s="32"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="32"/>
+    </row>
+    <row r="65" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>721</v>
+      </c>
+      <c r="C65" s="10"/>
+      <c r="D65" s="10"/>
+      <c r="E65" s="10"/>
+      <c r="F65" s="32" t="s">
+        <v>722</v>
+      </c>
+      <c r="G65" s="32"/>
+      <c r="H65" s="32"/>
+      <c r="I65" s="32"/>
+    </row>
+    <row r="66" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>724</v>
+      </c>
+      <c r="C66" s="10"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="10"/>
+      <c r="F66" s="32" t="s">
+        <v>725</v>
+      </c>
+      <c r="G66" s="32"/>
+      <c r="H66" s="32"/>
+      <c r="I66" s="32"/>
+    </row>
+    <row r="67" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="9" t="s">
+        <v>726</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>727</v>
+      </c>
+      <c r="C67" s="10"/>
+      <c r="D67" s="10"/>
+      <c r="E67" s="10"/>
+      <c r="F67" s="32" t="s">
+        <v>728</v>
+      </c>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="32"/>
+    </row>
+    <row r="68" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>729</v>
+      </c>
+      <c r="C68" s="10"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="10"/>
+      <c r="F68" s="32" t="s">
+        <v>730</v>
+      </c>
+      <c r="G68" s="32"/>
+      <c r="H68" s="32"/>
+      <c r="I68" s="32"/>
+    </row>
+    <row r="69" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>731</v>
+      </c>
+      <c r="C69" s="10"/>
+      <c r="D69" s="10"/>
+      <c r="E69" s="10"/>
+      <c r="F69" s="32" t="s">
+        <v>732</v>
+      </c>
+      <c r="G69" s="32"/>
+      <c r="H69" s="32"/>
+      <c r="I69" s="32"/>
+    </row>
+    <row r="70" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>734</v>
+      </c>
+      <c r="C70" s="10"/>
+      <c r="D70" s="10"/>
+      <c r="E70" s="10"/>
+      <c r="F70" s="32" t="s">
+        <v>735</v>
+      </c>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="32"/>
+    </row>
+    <row r="71" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>736</v>
+      </c>
+      <c r="C71" s="10"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="10"/>
+      <c r="F71" s="32" t="s">
+        <v>737</v>
+      </c>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
+    </row>
+    <row r="72" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="9" t="s">
+        <v>738</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>739</v>
+      </c>
+      <c r="C72" s="10"/>
+      <c r="D72" s="10"/>
+      <c r="E72" s="10"/>
+      <c r="F72" s="32" t="s">
+        <v>740</v>
+      </c>
+      <c r="G72" s="32"/>
+      <c r="H72" s="32"/>
+      <c r="I72" s="32"/>
+    </row>
+    <row r="73" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="85" t="s">
+        <v>741</v>
+      </c>
+      <c r="B73" s="86" t="s">
+        <v>742</v>
+      </c>
+      <c r="C73" s="86"/>
+      <c r="D73" s="86"/>
+      <c r="E73" s="86"/>
+      <c r="F73" s="87" t="s">
+        <v>743</v>
+      </c>
+      <c r="G73" s="87"/>
+      <c r="H73" s="87"/>
+      <c r="I73" s="87"/>
+    </row>
+    <row r="74" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>745</v>
+      </c>
+      <c r="C74" s="10"/>
+      <c r="D74" s="10"/>
+      <c r="E74" s="10"/>
+      <c r="F74" s="32" t="s">
+        <v>746</v>
+      </c>
+      <c r="G74" s="32"/>
+      <c r="H74" s="32"/>
+      <c r="I74" s="32"/>
+    </row>
+    <row r="76" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="38" t="s">
+        <v>747</v>
+      </c>
+      <c r="B76" s="38"/>
+      <c r="C76" s="38"/>
+      <c r="D76" s="38"/>
+      <c r="E76" s="38"/>
+      <c r="F76" s="38"/>
+      <c r="G76" s="38"/>
+      <c r="H76" s="38"/>
+      <c r="I76" s="38"/>
+    </row>
+    <row r="77" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="F77" s="8"/>
+      <c r="G77" s="8" t="s">
+        <v>748</v>
+      </c>
+      <c r="H77" s="8"/>
+      <c r="I77" s="8"/>
+    </row>
+    <row r="78" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="81" t="s">
+        <v>749</v>
+      </c>
+      <c r="B78" s="81"/>
+      <c r="C78" s="81"/>
+      <c r="D78" s="81"/>
+      <c r="E78" s="34"/>
+      <c r="F78" s="34"/>
+      <c r="G78" s="32" t="s">
+        <v>750</v>
+      </c>
+      <c r="H78" s="32"/>
+      <c r="I78" s="32"/>
+    </row>
+    <row r="79" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="81" t="s">
+        <v>751</v>
+      </c>
+      <c r="B79" s="81"/>
+      <c r="C79" s="81"/>
+      <c r="D79" s="81"/>
+      <c r="E79" s="34"/>
+      <c r="F79" s="34"/>
+      <c r="G79" s="32" t="s">
+        <v>752</v>
+      </c>
+      <c r="H79" s="32"/>
+      <c r="I79" s="32"/>
+    </row>
+    <row r="80" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="81" t="s">
+        <v>753</v>
+      </c>
+      <c r="B80" s="81"/>
+      <c r="C80" s="81"/>
+      <c r="D80" s="81"/>
+      <c r="E80" s="34"/>
+      <c r="F80" s="34"/>
+      <c r="G80" s="32" t="s">
+        <v>754</v>
+      </c>
+      <c r="H80" s="32"/>
+      <c r="I80" s="32"/>
+    </row>
+    <row r="81" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="81" t="s">
+        <v>755</v>
+      </c>
+      <c r="B81" s="81"/>
+      <c r="C81" s="81"/>
+      <c r="D81" s="81"/>
+      <c r="E81" s="34"/>
+      <c r="F81" s="34"/>
+      <c r="G81" s="32" t="s">
+        <v>756</v>
+      </c>
+      <c r="H81" s="32"/>
+      <c r="I81" s="32"/>
+    </row>
+    <row r="82" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="81" t="s">
+        <v>757</v>
+      </c>
+      <c r="B82" s="81"/>
+      <c r="C82" s="81"/>
+      <c r="D82" s="81"/>
+      <c r="E82" s="34"/>
+      <c r="F82" s="34"/>
+      <c r="G82" s="32" t="s">
+        <v>758</v>
+      </c>
+      <c r="H82" s="32"/>
+      <c r="I82" s="32"/>
+    </row>
+    <row r="84" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="18" t="s">
+        <v>759</v>
+      </c>
+      <c r="B84" s="18"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="18"/>
+      <c r="E84" s="18"/>
+      <c r="F84" s="18"/>
+      <c r="G84" s="18"/>
+      <c r="H84" s="18"/>
+      <c r="I84" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A18:F18"/>
+  <mergeCells count="75">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="F61:I61"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="F62:I62"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="B64:E64"/>
+    <mergeCell ref="F64:I64"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="F65:I65"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="F66:I66"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="F67:I67"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="F69:I69"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="F70:I70"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="F71:I71"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="F72:I72"/>
+    <mergeCell ref="B73:E73"/>
+    <mergeCell ref="F73:I73"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="F74:I74"/>
+    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="G77:I77"/>
+    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="G78:I78"/>
+    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="G79:I79"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="G80:I80"/>
+    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="G81:I81"/>
+    <mergeCell ref="A82:D82"/>
+    <mergeCell ref="E82:F82"/>
+    <mergeCell ref="G82:I82"/>
+    <mergeCell ref="A84:I84"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Escribe la respuesta textual, no tu interpretación. Las palabras exactas valen más después." promptTitle="Respuesta" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="D20:D53" type="none">
+  <conditionalFormatting sqref="E25:E58">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>"Respondida"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>"Parcial"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+      <formula>"Pendiente"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G25:G58">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+      <formula>"Alta"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="5">
+    <dataValidation allowBlank="true" error="Elige una de la lista." errorStyle="stop" errorTitle="Opción no válida" operator="between" prompt="Respondida = ya tienes la respuesta completa. Parcial = tienes parte y la respuesta dice qué falta. Pendiente = sin respuesta." promptTitle="Estado de la pregunta" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="E25:E58" type="list">
+      <formula1>"Respondida,Parcial,Pendiente"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Elige una de la lista." errorStyle="stop" errorTitle="Opción no válida" operator="between" prompt="Alta = pregúntala sí o sí. Ordena la reunión por esta columna." promptTitle="Prioridad para la reunión" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="G25:G58" type="list">
+      <formula1>"Alta,Media,Baja"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Escribe la respuesta textual, no tu interpretación. Si es parcial, termina la frase diciendo qué falta." promptTitle="Respuesta" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="D25:D58" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Quién lo dijo y cuándo. Una respuesta de la jefatura no equivale a una del operario." promptTitle="Fuente" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="F25:F58" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Anótala en la reunión, textual." promptTitle="Respuesta" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="E78:E82" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6518,7 +7803,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>679</v>
+        <v>760</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -6530,7 +7815,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>680</v>
+        <v>761</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -6542,7 +7827,7 @@
     </row>
     <row r="3" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E3" s="30" t="s">
-        <v>681</v>
+        <v>762</v>
       </c>
       <c r="F3" s="29" t="n">
         <f aca="false">IF(COUNTA($C$8:$C$31)=0,"",COUNTIF($G$8:$G$31,"Sí")/COUNTA($C$8:$C$31))</f>
@@ -6551,7 +7836,7 @@
     </row>
     <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>682</v>
+        <v>763</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -6566,7 +7851,7 @@
         <v>190</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>683</v>
+        <v>764</v>
       </c>
       <c r="C6" s="36"/>
       <c r="D6" s="36"/>
@@ -6580,22 +7865,22 @@
         <v>111</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>684</v>
+        <v>765</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>685</v>
+        <v>766</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>686</v>
+        <v>767</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>117</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>687</v>
+        <v>768</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>688</v>
+        <v>769</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>118</v>
@@ -6606,13 +7891,13 @@
         <v>1</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>689</v>
+        <v>770</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>690</v>
-      </c>
-      <c r="D8" s="77" t="s">
-        <v>691</v>
+        <v>771</v>
+      </c>
+      <c r="D8" s="88" t="s">
+        <v>772</v>
       </c>
       <c r="E8" s="34"/>
       <c r="F8" s="34"/>
@@ -6624,13 +7909,13 @@
         <v>2</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>689</v>
+        <v>770</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>692</v>
-      </c>
-      <c r="D9" s="77" t="s">
-        <v>691</v>
+        <v>773</v>
+      </c>
+      <c r="D9" s="88" t="s">
+        <v>772</v>
       </c>
       <c r="E9" s="34"/>
       <c r="F9" s="34"/>
@@ -6642,13 +7927,13 @@
         <v>3</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>689</v>
+        <v>770</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>693</v>
-      </c>
-      <c r="D10" s="77" t="s">
-        <v>691</v>
+        <v>774</v>
+      </c>
+      <c r="D10" s="88" t="s">
+        <v>772</v>
       </c>
       <c r="E10" s="34"/>
       <c r="F10" s="34"/>
@@ -6660,13 +7945,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>689</v>
+        <v>770</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>694</v>
-      </c>
-      <c r="D11" s="77" t="s">
-        <v>691</v>
+        <v>775</v>
+      </c>
+      <c r="D11" s="88" t="s">
+        <v>772</v>
       </c>
       <c r="E11" s="34"/>
       <c r="F11" s="34"/>
@@ -6678,13 +7963,13 @@
         <v>5</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>689</v>
+        <v>770</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>695</v>
-      </c>
-      <c r="D12" s="77" t="s">
-        <v>691</v>
+        <v>776</v>
+      </c>
+      <c r="D12" s="88" t="s">
+        <v>772</v>
       </c>
       <c r="E12" s="34"/>
       <c r="F12" s="34"/>
@@ -6696,13 +7981,13 @@
         <v>6</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>689</v>
+        <v>770</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>696</v>
-      </c>
-      <c r="D13" s="77" t="s">
-        <v>691</v>
+        <v>777</v>
+      </c>
+      <c r="D13" s="88" t="s">
+        <v>772</v>
       </c>
       <c r="E13" s="34"/>
       <c r="F13" s="34"/>
@@ -6714,13 +7999,13 @@
         <v>7</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>689</v>
+        <v>770</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>697</v>
-      </c>
-      <c r="D14" s="77" t="s">
-        <v>698</v>
+        <v>778</v>
+      </c>
+      <c r="D14" s="88" t="s">
+        <v>779</v>
       </c>
       <c r="E14" s="34"/>
       <c r="F14" s="34"/>
@@ -6732,13 +8017,13 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>689</v>
+        <v>770</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>699</v>
-      </c>
-      <c r="D15" s="77" t="s">
-        <v>698</v>
+        <v>780</v>
+      </c>
+      <c r="D15" s="88" t="s">
+        <v>779</v>
       </c>
       <c r="E15" s="34"/>
       <c r="F15" s="34"/>
@@ -6750,13 +8035,13 @@
         <v>9</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>689</v>
+        <v>770</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>700</v>
-      </c>
-      <c r="D16" s="77" t="s">
-        <v>691</v>
+        <v>781</v>
+      </c>
+      <c r="D16" s="88" t="s">
+        <v>772</v>
       </c>
       <c r="E16" s="34"/>
       <c r="F16" s="34"/>
@@ -6768,13 +8053,13 @@
         <v>10</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>689</v>
+        <v>770</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>701</v>
-      </c>
-      <c r="D17" s="77" t="s">
-        <v>698</v>
+        <v>782</v>
+      </c>
+      <c r="D17" s="88" t="s">
+        <v>779</v>
       </c>
       <c r="E17" s="34"/>
       <c r="F17" s="34"/>
@@ -6786,13 +8071,13 @@
         <v>11</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>702</v>
+        <v>783</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>703</v>
-      </c>
-      <c r="D18" s="77" t="s">
-        <v>691</v>
+        <v>784</v>
+      </c>
+      <c r="D18" s="88" t="s">
+        <v>772</v>
       </c>
       <c r="E18" s="34"/>
       <c r="F18" s="34"/>
@@ -6804,13 +8089,13 @@
         <v>12</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>702</v>
+        <v>783</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>704</v>
-      </c>
-      <c r="D19" s="77" t="s">
-        <v>691</v>
+        <v>785</v>
+      </c>
+      <c r="D19" s="88" t="s">
+        <v>772</v>
       </c>
       <c r="E19" s="34"/>
       <c r="F19" s="34"/>
@@ -6822,13 +8107,13 @@
         <v>13</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>705</v>
+        <v>786</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>706</v>
-      </c>
-      <c r="D20" s="77" t="s">
-        <v>691</v>
+        <v>787</v>
+      </c>
+      <c r="D20" s="88" t="s">
+        <v>772</v>
       </c>
       <c r="E20" s="34"/>
       <c r="F20" s="34"/>
@@ -6840,13 +8125,13 @@
         <v>14</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>705</v>
+        <v>786</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>707</v>
-      </c>
-      <c r="D21" s="77" t="s">
-        <v>698</v>
+        <v>788</v>
+      </c>
+      <c r="D21" s="88" t="s">
+        <v>779</v>
       </c>
       <c r="E21" s="34"/>
       <c r="F21" s="34"/>
@@ -6858,13 +8143,13 @@
         <v>15</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>705</v>
+        <v>786</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>708</v>
-      </c>
-      <c r="D22" s="77" t="s">
-        <v>709</v>
+        <v>789</v>
+      </c>
+      <c r="D22" s="88" t="s">
+        <v>790</v>
       </c>
       <c r="E22" s="34"/>
       <c r="F22" s="34"/>
@@ -6876,13 +8161,13 @@
         <v>16</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>710</v>
+        <v>791</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>711</v>
-      </c>
-      <c r="D23" s="77" t="s">
-        <v>709</v>
+        <v>792</v>
+      </c>
+      <c r="D23" s="88" t="s">
+        <v>790</v>
       </c>
       <c r="E23" s="34"/>
       <c r="F23" s="34"/>
@@ -6894,13 +8179,13 @@
         <v>17</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>710</v>
+        <v>791</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>712</v>
-      </c>
-      <c r="D24" s="77" t="s">
-        <v>698</v>
+        <v>793</v>
+      </c>
+      <c r="D24" s="88" t="s">
+        <v>779</v>
       </c>
       <c r="E24" s="34"/>
       <c r="F24" s="34"/>
@@ -6912,13 +8197,13 @@
         <v>18</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>674</v>
+        <v>704</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>713</v>
-      </c>
-      <c r="D25" s="77" t="s">
-        <v>698</v>
+        <v>794</v>
+      </c>
+      <c r="D25" s="88" t="s">
+        <v>779</v>
       </c>
       <c r="E25" s="34"/>
       <c r="F25" s="34"/>
@@ -6930,13 +8215,13 @@
         <v>19</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>674</v>
+        <v>704</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>714</v>
-      </c>
-      <c r="D26" s="77" t="s">
-        <v>698</v>
+        <v>795</v>
+      </c>
+      <c r="D26" s="88" t="s">
+        <v>779</v>
       </c>
       <c r="E26" s="34"/>
       <c r="F26" s="34"/>
@@ -6948,13 +8233,13 @@
         <v>20</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>674</v>
+        <v>704</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>715</v>
-      </c>
-      <c r="D27" s="77" t="s">
-        <v>698</v>
+        <v>796</v>
+      </c>
+      <c r="D27" s="88" t="s">
+        <v>779</v>
       </c>
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
@@ -6966,13 +8251,13 @@
         <v>21</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>716</v>
+        <v>797</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>717</v>
-      </c>
-      <c r="D28" s="77" t="s">
-        <v>691</v>
+        <v>798</v>
+      </c>
+      <c r="D28" s="88" t="s">
+        <v>772</v>
       </c>
       <c r="E28" s="34"/>
       <c r="F28" s="34"/>
@@ -6984,13 +8269,13 @@
         <v>22</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>716</v>
+        <v>797</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>718</v>
-      </c>
-      <c r="D29" s="77" t="s">
-        <v>698</v>
+        <v>799</v>
+      </c>
+      <c r="D29" s="88" t="s">
+        <v>779</v>
       </c>
       <c r="E29" s="34"/>
       <c r="F29" s="34"/>
@@ -7002,13 +8287,13 @@
         <v>23</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>719</v>
+        <v>800</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>720</v>
-      </c>
-      <c r="D30" s="77" t="s">
-        <v>721</v>
+        <v>801</v>
+      </c>
+      <c r="D30" s="88" t="s">
+        <v>802</v>
       </c>
       <c r="E30" s="34"/>
       <c r="F30" s="34"/>
@@ -7020,13 +8305,13 @@
         <v>24</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>722</v>
+        <v>803</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>723</v>
-      </c>
-      <c r="D31" s="77" t="s">
-        <v>698</v>
+        <v>804</v>
+      </c>
+      <c r="D31" s="88" t="s">
+        <v>779</v>
       </c>
       <c r="E31" s="34"/>
       <c r="F31" s="34"/>
@@ -7035,7 +8320,7 @@
     </row>
     <row r="33" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="18" t="s">
-        <v>724</v>
+        <v>805</v>
       </c>
       <c r="B33" s="18"/>
       <c r="C33" s="18"/>
@@ -7103,7 +8388,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>725</v>
+        <v>806</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -7115,7 +8400,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>726</v>
+        <v>807</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -7127,7 +8412,7 @@
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>727</v>
+        <v>808</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -7139,10 +8424,10 @@
     </row>
     <row r="5" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="39" t="s">
-        <v>728</v>
+        <v>809</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>729</v>
+        <v>810</v>
       </c>
       <c r="C5" s="36"/>
       <c r="D5" s="36"/>
@@ -7152,11 +8437,11 @@
       <c r="H5" s="36"/>
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="78" t="s">
-        <v>730</v>
+      <c r="A6" s="89" t="s">
+        <v>811</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>731</v>
+        <v>812</v>
       </c>
       <c r="C6" s="36"/>
       <c r="D6" s="36"/>
@@ -7170,22 +8455,22 @@
         <v>111</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>732</v>
+        <v>813</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>733</v>
+        <v>814</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>734</v>
+        <v>815</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>735</v>
+        <v>816</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>736</v>
+        <v>817</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>737</v>
+        <v>818</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>390</v>
@@ -7196,22 +8481,22 @@
         <v>304</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>738</v>
+        <v>819</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>739</v>
+        <v>820</v>
       </c>
       <c r="D9" s="40" t="s">
-        <v>740</v>
+        <v>821</v>
       </c>
       <c r="E9" s="40" t="s">
-        <v>741</v>
+        <v>822</v>
       </c>
       <c r="F9" s="40" t="s">
         <v>9</v>
       </c>
       <c r="G9" s="40" t="s">
-        <v>742</v>
+        <v>823</v>
       </c>
       <c r="H9" s="40" t="s">
         <v>407</v>
@@ -7399,7 +8684,7 @@
     </row>
     <row r="26" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="s">
-        <v>743</v>
+        <v>824</v>
       </c>
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
@@ -7484,7 +8769,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>744</v>
+        <v>825</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -7497,7 +8782,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>745</v>
+        <v>826</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -7526,7 +8811,7 @@
         <v>168</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>746</v>
+        <v>827</v>
       </c>
       <c r="C5" s="36"/>
       <c r="D5" s="36"/>
@@ -7541,7 +8826,7 @@
         <v>170</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>747</v>
+        <v>828</v>
       </c>
       <c r="C6" s="36"/>
       <c r="D6" s="36"/>
@@ -7556,7 +8841,7 @@
         <v>172</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>748</v>
+        <v>829</v>
       </c>
       <c r="C7" s="36"/>
       <c r="D7" s="36"/>
@@ -7571,7 +8856,7 @@
         <v>174</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>749</v>
+        <v>830</v>
       </c>
       <c r="C8" s="36"/>
       <c r="D8" s="36"/>
@@ -7599,7 +8884,7 @@
         <v>177</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>750</v>
+        <v>831</v>
       </c>
       <c r="C10" s="36"/>
       <c r="D10" s="36"/>
@@ -7614,7 +8899,7 @@
         <v>179</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>751</v>
+        <v>832</v>
       </c>
       <c r="C11" s="36"/>
       <c r="D11" s="36"/>
@@ -7629,7 +8914,7 @@
         <v>181</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>752</v>
+        <v>833</v>
       </c>
       <c r="C12" s="36"/>
       <c r="D12" s="36"/>
@@ -7644,7 +8929,7 @@
         <v>183</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>753</v>
+        <v>834</v>
       </c>
       <c r="C13" s="36"/>
       <c r="D13" s="36"/>
@@ -7659,7 +8944,7 @@
         <v>185</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>754</v>
+        <v>835</v>
       </c>
       <c r="C14" s="36"/>
       <c r="D14" s="36"/>
@@ -7674,7 +8959,7 @@
         <v>187</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>755</v>
+        <v>836</v>
       </c>
       <c r="C15" s="36"/>
       <c r="D15" s="36"/>
@@ -7702,7 +8987,7 @@
         <v>190</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>756</v>
+        <v>837</v>
       </c>
       <c r="C17" s="36"/>
       <c r="D17" s="36"/>
@@ -7717,7 +9002,7 @@
         <v>190</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>757</v>
+        <v>838</v>
       </c>
       <c r="C18" s="36"/>
       <c r="D18" s="36"/>
@@ -7732,7 +9017,7 @@
         <v>190</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>758</v>
+        <v>839</v>
       </c>
       <c r="C19" s="36"/>
       <c r="D19" s="36"/>
@@ -7747,7 +9032,7 @@
         <v>190</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>759</v>
+        <v>840</v>
       </c>
       <c r="C20" s="36"/>
       <c r="D20" s="36"/>
@@ -7762,7 +9047,7 @@
         <v>190</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>760</v>
+        <v>841</v>
       </c>
       <c r="C21" s="36"/>
       <c r="D21" s="36"/>
@@ -7777,7 +9062,7 @@
         <v>190</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>761</v>
+        <v>842</v>
       </c>
       <c r="C22" s="36"/>
       <c r="D22" s="36"/>
@@ -7805,7 +9090,7 @@
         <v>197</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>762</v>
+        <v>843</v>
       </c>
       <c r="C24" s="36"/>
       <c r="D24" s="36"/>
@@ -7820,7 +9105,7 @@
         <v>197</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>763</v>
+        <v>844</v>
       </c>
       <c r="C25" s="36"/>
       <c r="D25" s="36"/>
@@ -7835,7 +9120,7 @@
         <v>197</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>764</v>
+        <v>845</v>
       </c>
       <c r="C26" s="36"/>
       <c r="D26" s="36"/>
@@ -7850,7 +9135,7 @@
         <v>197</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>765</v>
+        <v>846</v>
       </c>
       <c r="C27" s="36"/>
       <c r="D27" s="36"/>
@@ -7865,7 +9150,7 @@
         <v>197</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>766</v>
+        <v>847</v>
       </c>
       <c r="C28" s="36"/>
       <c r="D28" s="36"/>
@@ -7877,28 +9162,28 @@
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>767</v>
+        <v>848</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>768</v>
+        <v>849</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>769</v>
+        <v>850</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>770</v>
+        <v>851</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>771</v>
+        <v>852</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>772</v>
+        <v>853</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>773</v>
+        <v>854</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>774</v>
+        <v>855</v>
       </c>
       <c r="I30" s="8" t="s">
         <v>118</v>
@@ -7906,142 +9191,142 @@
     </row>
     <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="40" t="s">
-        <v>775</v>
+        <v>856</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>776</v>
+        <v>857</v>
       </c>
       <c r="C31" s="41" t="n">
         <v>0.026</v>
       </c>
       <c r="D31" s="40" t="s">
-        <v>777</v>
+        <v>858</v>
       </c>
       <c r="E31" s="40" t="s">
         <v>9</v>
       </c>
       <c r="F31" s="40" t="s">
-        <v>778</v>
+        <v>859</v>
       </c>
       <c r="G31" s="40" t="s">
-        <v>778</v>
+        <v>859</v>
       </c>
       <c r="H31" s="40" t="s">
-        <v>779</v>
+        <v>860</v>
       </c>
       <c r="I31" s="40" t="s">
-        <v>780</v>
+        <v>861</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="76" t="s">
-        <v>781</v>
+      <c r="A32" s="81" t="s">
+        <v>862</v>
       </c>
       <c r="B32" s="34" t="s">
-        <v>782</v>
-      </c>
-      <c r="C32" s="79"/>
+        <v>863</v>
+      </c>
+      <c r="C32" s="90"/>
       <c r="D32" s="33"/>
       <c r="E32" s="34"/>
-      <c r="F32" s="80" t="s">
-        <v>778</v>
-      </c>
-      <c r="G32" s="81" t="s">
-        <v>778</v>
+      <c r="F32" s="91" t="s">
+        <v>859</v>
+      </c>
+      <c r="G32" s="92" t="s">
+        <v>859</v>
       </c>
       <c r="H32" s="33"/>
-      <c r="I32" s="82" t="s">
-        <v>783</v>
+      <c r="I32" s="93" t="s">
+        <v>864</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="76" t="s">
-        <v>784</v>
+      <c r="A33" s="81" t="s">
+        <v>865</v>
       </c>
       <c r="B33" s="34" t="s">
-        <v>785</v>
-      </c>
-      <c r="C33" s="79"/>
+        <v>866</v>
+      </c>
+      <c r="C33" s="90"/>
       <c r="D33" s="33"/>
       <c r="E33" s="34"/>
-      <c r="F33" s="83" t="str">
+      <c r="F33" s="94" t="str">
         <f aca="false">IF('4 Conteo ciego'!$F$27="","",'4 Conteo ciego'!$F$27)</f>
         <v/>
       </c>
-      <c r="G33" s="81" t="s">
-        <v>778</v>
+      <c r="G33" s="92" t="s">
+        <v>859</v>
       </c>
       <c r="H33" s="33"/>
-      <c r="I33" s="82" t="s">
-        <v>786</v>
+      <c r="I33" s="93" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="76" t="s">
-        <v>787</v>
+      <c r="A34" s="81" t="s">
+        <v>868</v>
       </c>
       <c r="B34" s="34" t="s">
-        <v>788</v>
-      </c>
-      <c r="C34" s="79"/>
+        <v>869</v>
+      </c>
+      <c r="C34" s="90"/>
       <c r="D34" s="33"/>
       <c r="E34" s="34"/>
-      <c r="F34" s="83" t="str">
+      <c r="F34" s="94" t="str">
         <f aca="false">IF('2 Ocupación y piso'!$G$42="","",'2 Ocupación y piso'!$G$42)</f>
         <v/>
       </c>
-      <c r="G34" s="81" t="s">
-        <v>778</v>
+      <c r="G34" s="92" t="s">
+        <v>859</v>
       </c>
       <c r="H34" s="33"/>
-      <c r="I34" s="82" t="s">
-        <v>789</v>
+      <c r="I34" s="93" t="s">
+        <v>870</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="76" t="s">
-        <v>790</v>
+      <c r="A35" s="81" t="s">
+        <v>871</v>
       </c>
       <c r="B35" s="34" t="s">
-        <v>791</v>
-      </c>
-      <c r="C35" s="79"/>
+        <v>872</v>
+      </c>
+      <c r="C35" s="90"/>
       <c r="D35" s="33"/>
       <c r="E35" s="34"/>
-      <c r="F35" s="83" t="str">
+      <c r="F35" s="94" t="str">
         <f aca="false">IF('2 Ocupación y piso'!$F$42="","",'2 Ocupación y piso'!$F$42)</f>
         <v/>
       </c>
-      <c r="G35" s="84" t="str">
+      <c r="G35" s="95" t="str">
         <f aca="false">IF(OR($C35="",$F35=""),"",$C35-$F35)</f>
         <v/>
       </c>
       <c r="H35" s="33"/>
-      <c r="I35" s="82" t="s">
-        <v>792</v>
+      <c r="I35" s="93" t="s">
+        <v>873</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="76" t="s">
-        <v>793</v>
+      <c r="A36" s="81" t="s">
+        <v>874</v>
       </c>
       <c r="B36" s="34" t="s">
-        <v>794</v>
-      </c>
-      <c r="C36" s="85"/>
+        <v>875</v>
+      </c>
+      <c r="C36" s="96"/>
       <c r="D36" s="33"/>
       <c r="E36" s="34"/>
       <c r="F36" s="65" t="str">
         <f aca="false">IF('6 Seguimiento pedidos'!$Q$94="","",'6 Seguimiento pedidos'!$Q$94)</f>
         <v/>
       </c>
-      <c r="G36" s="86" t="str">
+      <c r="G36" s="97" t="str">
         <f aca="false">IF(OR($C36="",$F36=""),"",$C36-$F36)</f>
         <v/>
       </c>
       <c r="H36" s="33"/>
-      <c r="I36" s="82" t="s">
-        <v>795</v>
+      <c r="I36" s="93" t="s">
+        <v>876</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8056,7 +9341,7 @@
         <v/>
       </c>
       <c r="H37" s="33"/>
-      <c r="I37" s="82"/>
+      <c r="I37" s="93"/>
     </row>
     <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="34"/>
@@ -8070,7 +9355,7 @@
         <v/>
       </c>
       <c r="H38" s="33"/>
-      <c r="I38" s="82"/>
+      <c r="I38" s="93"/>
     </row>
     <row r="39" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="34"/>
@@ -8084,7 +9369,7 @@
         <v/>
       </c>
       <c r="H39" s="33"/>
-      <c r="I39" s="82"/>
+      <c r="I39" s="93"/>
     </row>
     <row r="40" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="34"/>
@@ -8098,7 +9383,7 @@
         <v/>
       </c>
       <c r="H40" s="33"/>
-      <c r="I40" s="82"/>
+      <c r="I40" s="93"/>
     </row>
     <row r="41" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="34"/>
@@ -8112,11 +9397,11 @@
         <v/>
       </c>
       <c r="H41" s="33"/>
-      <c r="I41" s="82"/>
+      <c r="I41" s="93"/>
     </row>
     <row r="43" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="18" t="s">
-        <v>796</v>
+        <v>877</v>
       </c>
       <c r="B43" s="18"/>
       <c r="C43" s="18"/>
@@ -8228,456 +9513,456 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>797</v>
+        <v>878</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>798</v>
+        <v>879</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>799</v>
+        <v>880</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>67</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>800</v>
+        <v>881</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="87" t="s">
-        <v>801</v>
+      <c r="A5" s="98" t="s">
+        <v>882</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>802</v>
+        <v>883</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>803</v>
+        <v>884</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="98" t="s">
         <v>299</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>804</v>
+        <v>885</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>805</v>
+        <v>886</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="87" t="s">
-        <v>806</v>
+      <c r="A7" s="98" t="s">
+        <v>887</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>807</v>
+        <v>888</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>808</v>
+        <v>889</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="87" t="s">
-        <v>809</v>
+      <c r="A8" s="98" t="s">
+        <v>890</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>810</v>
+        <v>891</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>811</v>
+        <v>892</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="87" t="s">
-        <v>812</v>
+      <c r="A9" s="98" t="s">
+        <v>893</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>813</v>
+        <v>894</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>814</v>
+        <v>895</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="87" t="s">
-        <v>815</v>
+      <c r="A10" s="98" t="s">
+        <v>896</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>816</v>
+        <v>897</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>817</v>
+        <v>898</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="87" t="s">
-        <v>818</v>
+      <c r="A11" s="98" t="s">
+        <v>899</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>819</v>
+        <v>900</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>820</v>
+        <v>901</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="87" t="s">
-        <v>821</v>
+      <c r="A12" s="98" t="s">
+        <v>902</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>822</v>
+        <v>903</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>823</v>
+        <v>904</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="87" t="s">
-        <v>824</v>
+      <c r="A13" s="98" t="s">
+        <v>905</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>825</v>
+        <v>906</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>826</v>
+        <v>907</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="87" t="s">
-        <v>827</v>
+      <c r="A14" s="98" t="s">
+        <v>908</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>828</v>
+        <v>909</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>829</v>
+        <v>910</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="87" t="s">
-        <v>830</v>
+      <c r="A15" s="98" t="s">
+        <v>911</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>831</v>
+        <v>912</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>832</v>
+        <v>913</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="87" t="s">
-        <v>833</v>
+      <c r="A16" s="98" t="s">
+        <v>914</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>834</v>
+        <v>915</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>835</v>
+        <v>916</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="87" t="s">
-        <v>836</v>
+      <c r="A17" s="98" t="s">
+        <v>917</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>837</v>
+        <v>918</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>838</v>
+        <v>919</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="87" t="s">
-        <v>542</v>
+      <c r="A18" s="98" t="s">
+        <v>550</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>839</v>
+        <v>920</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>840</v>
+        <v>921</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="87" t="s">
-        <v>841</v>
+      <c r="A19" s="98" t="s">
+        <v>922</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>842</v>
+        <v>923</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>843</v>
+        <v>924</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="87" t="s">
-        <v>844</v>
+      <c r="A20" s="98" t="s">
+        <v>925</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>845</v>
+        <v>926</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>846</v>
+        <v>927</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="87" t="s">
-        <v>847</v>
+      <c r="A21" s="98" t="s">
+        <v>928</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>848</v>
+        <v>929</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>849</v>
+        <v>930</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="87" t="s">
-        <v>850</v>
+      <c r="A22" s="98" t="s">
+        <v>931</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>851</v>
+        <v>932</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>852</v>
+        <v>933</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="87" t="s">
-        <v>853</v>
+      <c r="A23" s="98" t="s">
+        <v>934</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>854</v>
+        <v>935</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>855</v>
+        <v>936</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="87" t="s">
-        <v>856</v>
+      <c r="A24" s="98" t="s">
+        <v>937</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>857</v>
+        <v>938</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>858</v>
+        <v>939</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="87" t="s">
-        <v>859</v>
+      <c r="A25" s="98" t="s">
+        <v>940</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>860</v>
+        <v>941</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>861</v>
+        <v>942</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="87" t="s">
-        <v>862</v>
+      <c r="A26" s="98" t="s">
+        <v>943</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>863</v>
+        <v>944</v>
       </c>
       <c r="C26" s="32" t="s">
-        <v>864</v>
+        <v>945</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="87" t="s">
-        <v>865</v>
+      <c r="A27" s="98" t="s">
+        <v>946</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>866</v>
+        <v>947</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>867</v>
+        <v>948</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="87" t="s">
-        <v>868</v>
+      <c r="A28" s="98" t="s">
+        <v>949</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>869</v>
+        <v>950</v>
       </c>
       <c r="C28" s="32" t="s">
-        <v>870</v>
+        <v>951</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="87" t="s">
-        <v>871</v>
+      <c r="A29" s="98" t="s">
+        <v>952</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>872</v>
+        <v>953</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>873</v>
+        <v>954</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="87" t="s">
-        <v>874</v>
+      <c r="A30" s="98" t="s">
+        <v>955</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>875</v>
+        <v>956</v>
       </c>
       <c r="C30" s="32" t="s">
-        <v>876</v>
+        <v>957</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="87" t="s">
-        <v>877</v>
+      <c r="A31" s="98" t="s">
+        <v>958</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>878</v>
+        <v>959</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>879</v>
+        <v>960</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="87" t="s">
-        <v>880</v>
+      <c r="A32" s="98" t="s">
+        <v>961</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>881</v>
+        <v>962</v>
       </c>
       <c r="C32" s="32" t="s">
-        <v>882</v>
+        <v>963</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="87" t="s">
-        <v>883</v>
+      <c r="A33" s="98" t="s">
+        <v>964</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>884</v>
+        <v>965</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>885</v>
+        <v>966</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="87" t="s">
-        <v>886</v>
+      <c r="A34" s="98" t="s">
+        <v>967</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>887</v>
+        <v>968</v>
       </c>
       <c r="C34" s="32" t="s">
-        <v>888</v>
+        <v>969</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="87" t="s">
+      <c r="A35" s="98" t="s">
         <v>389</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>889</v>
+        <v>970</v>
       </c>
       <c r="C35" s="32" t="s">
-        <v>890</v>
+        <v>971</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="87" t="s">
-        <v>891</v>
+      <c r="A36" s="98" t="s">
+        <v>972</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>892</v>
+        <v>973</v>
       </c>
       <c r="C36" s="32" t="s">
-        <v>893</v>
+        <v>974</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="87" t="s">
-        <v>894</v>
+      <c r="A37" s="98" t="s">
+        <v>975</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>895</v>
+        <v>976</v>
       </c>
       <c r="C37" s="32" t="s">
-        <v>896</v>
+        <v>977</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="87" t="s">
-        <v>897</v>
+      <c r="A38" s="98" t="s">
+        <v>714</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>898</v>
+        <v>978</v>
       </c>
       <c r="C38" s="32" t="s">
-        <v>899</v>
+        <v>979</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="87" t="s">
-        <v>900</v>
+      <c r="A39" s="98" t="s">
+        <v>980</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>901</v>
+        <v>981</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>902</v>
+        <v>982</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="87" t="s">
-        <v>903</v>
+      <c r="A40" s="98" t="s">
+        <v>983</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>904</v>
+        <v>984</v>
       </c>
       <c r="C40" s="32" t="s">
-        <v>905</v>
+        <v>985</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="87" t="s">
-        <v>906</v>
+      <c r="A41" s="98" t="s">
+        <v>986</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>907</v>
+        <v>987</v>
       </c>
       <c r="C41" s="32" t="s">
-        <v>908</v>
+        <v>988</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="87" t="s">
-        <v>909</v>
+      <c r="A42" s="98" t="s">
+        <v>989</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>910</v>
+        <v>990</v>
       </c>
       <c r="C42" s="32" t="s">
-        <v>911</v>
+        <v>991</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="87" t="s">
-        <v>912</v>
+      <c r="A43" s="98" t="s">
+        <v>992</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>913</v>
+        <v>993</v>
       </c>
       <c r="C43" s="32" t="s">
-        <v>914</v>
+        <v>994</v>
       </c>
     </row>
   </sheetData>
